--- a/data/trans_camb/IP7_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP7_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,67</t>
+          <t>-0,86; 3,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,0</t>
+          <t>-2,48; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 6,42</t>
+          <t>-0,04; 6,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -0,7</t>
+          <t>-6,35; -0,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 1,33</t>
+          <t>-5,42; 1,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 2,46</t>
+          <t>-4,71; 2,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,42</t>
+          <t>-2,95; 0,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 0,72</t>
+          <t>-2,64; 0,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,74</t>
+          <t>-1,43; 3,14</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 397,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-78,21; 439,96</t>
+          <t>-75,96; 613,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 1,33</t>
+          <t>-5,33; 1,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,54</t>
+          <t>-5,64; 0,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 4,91</t>
+          <t>-2,81; 5,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 1,78</t>
+          <t>-5,51; 1,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 2,5</t>
+          <t>-4,75; 2,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 5,4</t>
+          <t>-3,4; 5,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,94</t>
+          <t>-3,88; 0,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 0,87</t>
+          <t>-3,88; 0,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,14</t>
+          <t>-1,91; 3,98</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,81; 144,29</t>
+          <t>-91,54; 109,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-92,18; 112,89</t>
+          <t>-92,54; 96,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,98; 417,39</t>
+          <t>-64,13; 338,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 3,06</t>
+          <t>-2,09; 3,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 8,8</t>
+          <t>-0,47; 8,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,0</t>
+          <t>-4,64; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,49; -1,26</t>
+          <t>-7,71; -1,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 2,0</t>
+          <t>-5,73; 1,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 4,6</t>
+          <t>-4,69; 4,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,26</t>
+          <t>-4,09; 0,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 3,24</t>
+          <t>-2,78; 3,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 1,85</t>
+          <t>-3,52; 2,09</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 163,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,57; 361,1</t>
+          <t>-83,66; 296,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 330,25</t>
+          <t>-100,0; 289,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,99</t>
+          <t>-0,86; 3,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,52</t>
+          <t>-2,05; 2,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 12,33</t>
+          <t>-0,77; 14,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,52</t>
+          <t>-0,77; 4,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 3,2</t>
+          <t>-2,07; 3,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,69</t>
+          <t>-2,01; 2,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,47</t>
+          <t>-0,01; 3,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,16</t>
+          <t>-1,15; 2,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 6,09</t>
+          <t>-0,63; 6,17</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,56; 552,6</t>
+          <t>-48,83; 570,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-73,83; 515,65</t>
+          <t>-76,08; 378,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,76; 2301,34</t>
+          <t>-51,59; inf</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 407,26</t>
+          <t>-27,32; 373,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,99; 282,27</t>
+          <t>-62,31; 290,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,58; 243,64</t>
+          <t>-62,74; 237,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 288,72</t>
+          <t>-8,23; 295,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,93; 163,26</t>
+          <t>-45,84; 184,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 472,18</t>
+          <t>-33,78; 443,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 3,81</t>
+          <t>-3,0; 3,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 5,03</t>
+          <t>-2,09; 4,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 4,1</t>
+          <t>-2,93; 4,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 0,67</t>
+          <t>-6,61; 0,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 0,9</t>
+          <t>-6,66; 1,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 1,11</t>
+          <t>-6,31; 0,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1,23</t>
+          <t>-3,81; 1,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 1,69</t>
+          <t>-3,38; 1,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,38</t>
+          <t>-3,77; 1,53</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-73,22; 459,16</t>
+          <t>-75,35; 565,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-60,14; 716,85</t>
+          <t>-61,05; 652,1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-77,99; 641,58</t>
+          <t>-81,92; 676,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-88,12; 54,58</t>
+          <t>-89,43; 67,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-87,98; 58,28</t>
+          <t>-87,99; 67,44</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-85,54; 66,47</t>
+          <t>-89,42; 59,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-73,14; 56,69</t>
+          <t>-74,73; 55,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-62,58; 79,72</t>
+          <t>-64,01; 84,66</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-70,5; 67,11</t>
+          <t>-72,0; 71,81</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,77; 12,91</t>
+          <t>0,72; 12,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 5,24</t>
+          <t>-0,8; 6,15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,13; 8,78</t>
+          <t>-0,08; 8,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 1,7</t>
+          <t>-8,32; 1,78</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -0,5</t>
+          <t>-9,62; -0,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 3,71</t>
+          <t>-7,57; 3,05</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 4,55</t>
+          <t>-2,66; 4,64</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 1,09</t>
+          <t>-4,68; 1,17</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 3,97</t>
+          <t>-2,92; 4,08</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 110,52</t>
+          <t>-100,0; 109,87</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 98,45</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 217,64</t>
+          <t>-100,0; 220,02</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-64,74; 287,58</t>
+          <t>-62,03; 337,84</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 122,16</t>
+          <t>-100,0; 167,29</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-65,0; 280,21</t>
+          <t>-76,71; 237,91</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,2</t>
+          <t>-0,32; 2,2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,81</t>
+          <t>-0,62; 1,6</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,2; 5,34</t>
+          <t>0,3; 5,01</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,19</t>
+          <t>-2,59; 0,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,09</t>
+          <t>-2,66; 0,09</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,56</t>
+          <t>-2,37; 0,65</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,87</t>
+          <t>-1,1; 0,76</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,57</t>
+          <t>-1,32; 0,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,94</t>
+          <t>-0,78; 1,89</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 218,94</t>
+          <t>-17,45; 201,58</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 185,91</t>
+          <t>-30,96; 156,09</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5,15; 498,6</t>
+          <t>2,39; 418,55</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-60,34; 9,49</t>
+          <t>-61,87; 16,86</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-67,18; 5,23</t>
+          <t>-63,78; 5,77</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-57,63; 22,73</t>
+          <t>-57,66; 26,22</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 46,7</t>
+          <t>-37,02; 39,04</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 28,45</t>
+          <t>-44,53; 30,23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-27,94; 97,72</t>
+          <t>-27,41; 87,43</t>
         </is>
       </c>
     </row>
